--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2018.xlsx
@@ -15543,7 +15543,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Tasa de matrícula población de 0 a 24 años</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2018.xlsx
@@ -462,7 +462,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5108,7 +5108,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -10352,7 +10352,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -10628,7 +10628,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -15642,7 +15642,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -15688,7 +15688,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -15734,7 +15734,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -15780,7 +15780,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2018.xlsx
@@ -2128,7 +2128,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:34</t>
+    <t xml:space="preserve">2026-09-07 12:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2018.xlsx
@@ -2128,7 +2128,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:48</t>
+    <t xml:space="preserve">2026-09-08 10:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
